--- a/diseases/d099/2000-2004.xlsx
+++ b/diseases/d099/2000-2004.xlsx
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -21732,7 +21732,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -24867,7 +24867,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -25912,7 +25912,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -28634,7 +28634,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -30724,7 +30724,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -31769,7 +31769,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -33859,7 +33859,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -34904,7 +34904,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -35949,7 +35949,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -36994,7 +36994,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -38039,7 +38039,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -39084,7 +39084,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -40129,7 +40129,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -41806,7 +41806,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -42851,7 +42851,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -44941,7 +44941,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -45986,7 +45986,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -48076,7 +48076,7 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -49121,7 +49121,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -50166,7 +50166,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -51211,7 +51211,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -52256,7 +52256,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -53301,7 +53301,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -54978,7 +54978,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -56023,7 +56023,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -57068,7 +57068,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -58113,7 +58113,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -59158,7 +59158,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -60203,7 +60203,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -61248,7 +61248,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -62293,7 +62293,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -63338,7 +63338,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -64383,7 +64383,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -65428,7 +65428,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -66473,7 +66473,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">

--- a/diseases/d099/2000-2004.xlsx
+++ b/diseases/d099/2000-2004.xlsx
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -21732,7 +21732,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -24867,7 +24867,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -25912,7 +25912,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -28634,7 +28634,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -30724,7 +30724,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -31769,7 +31769,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -33859,7 +33859,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -34904,7 +34904,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -35949,7 +35949,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -36994,7 +36994,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -38039,7 +38039,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -39084,7 +39084,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -40129,7 +40129,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -41806,7 +41806,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -42851,7 +42851,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -44941,7 +44941,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -45986,7 +45986,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -48076,7 +48076,7 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -49121,7 +49121,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -50166,7 +50166,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -51211,7 +51211,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -52256,7 +52256,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -53301,7 +53301,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -54978,7 +54978,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -56023,7 +56023,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -57068,7 +57068,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -58113,7 +58113,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -59158,7 +59158,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -60203,7 +60203,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -61248,7 +61248,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -62293,7 +62293,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -63338,7 +63338,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -64383,7 +64383,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -65428,7 +65428,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -66473,7 +66473,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">
